--- a/TP2/matriz_correlaciones_TP2.xlsx
+++ b/TP2/matriz_correlaciones_TP2.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Corr_2024" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Corr_2025" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pval_2024" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Pval_2025" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Diferencia" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -440,7 +443,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Horas trabajadas (jefe/a)</t>
+          <t>Horas trabajadas (jefe)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -487,7 +490,7 @@
         <v>-0.25</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.15</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="3">
@@ -518,7 +521,7 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="4">
@@ -549,7 +552,7 @@
         <v>0.1</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -580,13 +583,13 @@
         <v>0.3</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Horas trabajadas (jefe/a)</t>
+          <t>Horas trabajadas (jefe)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -611,7 +614,7 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -642,7 +645,7 @@
         <v>-0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="8">
@@ -673,7 +676,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="9">
@@ -683,25 +686,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.15</v>
+        <v>-0.35</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05</v>
+        <v>0.29</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05</v>
+        <v>0.38</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -744,7 +747,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Horas trabajadas (jefe/a)</t>
+          <t>Horas trabajadas (jefe)</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -791,7 +794,7 @@
         <v>-0.22</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.16</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="3">
@@ -822,7 +825,7 @@
         <v>0.12</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +856,7 @@
         <v>0.09</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -884,13 +887,13 @@
         <v>0.29</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Horas trabajadas (jefe/a)</t>
+          <t>Horas trabajadas (jefe)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -915,7 +918,7 @@
         <v>0.14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -946,7 +949,7 @@
         <v>-0.14</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
     </row>
     <row r="8">
@@ -977,7 +980,7 @@
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="9">
@@ -987,28 +990,940 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.16</v>
+        <v>-0.33</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04</v>
+        <v>0.31</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Informalidad</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Edad al cuadrado</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Años de educación</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Horas trabajadas (jefe)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Miembros del hogar</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ingreso ocupación principal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tamaño del establecimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Informalidad</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Edad al cuadrado</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Años de educación</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Horas trabajadas (jefe)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Miembros del hogar</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ingreso ocupación principal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tamaño del establecimiento</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Informalidad</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Edad al cuadrado</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Años de educación</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Horas trabajadas (jefe)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Miembros del hogar</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ingreso ocupación principal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tamaño del establecimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Informalidad</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Edad al cuadrado</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Años de educación</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Horas trabajadas (jefe)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Miembros del hogar</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ingreso ocupación principal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tamaño del establecimiento</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Informalidad</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Edad al cuadrado</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Años de educación</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Horas trabajadas (jefe)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Miembros del hogar</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Ingreso ocupación principal</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Tamaño del establecimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Informalidad</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.015</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Edad</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.004</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Edad al cuadrado</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-0.005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Años de educación</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Horas trabajadas (jefe)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.024</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.038</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Miembros del hogar</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.008999999999999999</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ingreso ocupación principal</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.065</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tamaño del establecimiento</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.038</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.065</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
